--- a/Stats Sheet/Round Gaps/Zoinks.xlsx
+++ b/Stats Sheet/Round Gaps/Zoinks.xlsx
@@ -43,6 +43,9 @@
     <x:t>8b</x:t>
   </x:si>
   <x:si>
+    <x:t>9a</x:t>
+  </x:si>
+  <x:si>
     <x:t>_Fost_</x:t>
   </x:si>
   <x:si>
@@ -88,6 +91,9 @@
     <x:t>486</x:t>
   </x:si>
   <x:si>
+    <x:t>93</x:t>
+  </x:si>
+  <x:si>
     <x:t>omchris</x:t>
   </x:si>
   <x:si>
@@ -139,6 +145,9 @@
     <x:t>1madlilgrunt</x:t>
   </x:si>
   <x:si>
+    <x:t>377</x:t>
+  </x:si>
+  <x:si>
     <x:t>Buzzy_Bee_120</x:t>
   </x:si>
   <x:si>
@@ -157,6 +166,9 @@
     <x:t>WackoFlipper</x:t>
   </x:si>
   <x:si>
+    <x:t>957</x:t>
+  </x:si>
+  <x:si>
     <x:t>Codwhy</x:t>
   </x:si>
   <x:si>
@@ -184,6 +196,9 @@
     <x:t>SpaceFenix</x:t>
   </x:si>
   <x:si>
+    <x:t>294</x:t>
+  </x:si>
+  <x:si>
     <x:t>Flohp</x:t>
   </x:si>
   <x:si>
@@ -209,6 +224,18 @@
   </x:si>
   <x:si>
     <x:t>Keelando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CrowJRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JaeHasNoMaidens</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pierce981</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Queequa</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -567,10 +594,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:M46"/>
+  <x:dimension ref="A1:N50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:13" s="1" customFormat="1">
+    <x:row r="1" spans="1:14" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>45019</x:v>
       </x:c>
@@ -598,8 +625,11 @@
       <x:c r="M1" s="1">
         <x:v>46038</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:13">
+      <x:c r="N1" s="1">
+        <x:v>46126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14">
       <x:c r="F2" s="0">
         <x:v>119</x:v>
       </x:c>
@@ -624,8 +654,11 @@
       <x:c r="M2" s="0">
         <x:v>5</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:13">
+      <x:c r="N2" s="0">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -653,13 +686,16 @@
       <x:c r="M3" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:13">
+      <x:c r="N3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
@@ -668,27 +704,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:14">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
@@ -697,15 +733,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
@@ -714,59 +750,62 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:13">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -775,68 +814,71 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -845,103 +887,109 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:13">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:14">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:13">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:14">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:14">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
@@ -950,47 +998,50 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:13">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:14">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:13">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:14">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
@@ -999,53 +1050,56 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:14">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M16" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:14">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
@@ -1054,18 +1108,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:13">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:14">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
@@ -1074,50 +1128,53 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:13">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:14">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M19" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:14">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>1</x:v>
@@ -1126,111 +1183,120 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:13">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:14">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:13">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N21" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:14">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:13">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N22" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:14">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:14">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>2</x:v>
@@ -1239,15 +1305,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:14">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>2</x:v>
@@ -1256,21 +1322,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:14">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>2</x:v>
@@ -1279,93 +1345,102 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:14">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L27" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M27" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:14">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:14">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L29" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="M29" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:14">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>3</x:v>
@@ -1374,76 +1449,82 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:14">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M31" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N31" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:14">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M32" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N32" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:14">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>4</x:v>
@@ -1452,18 +1533,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:14">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>4</x:v>
@@ -1472,18 +1553,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L34" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:13">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:14">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>5</x:v>
@@ -1492,15 +1573,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:14">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>5</x:v>
@@ -1509,44 +1590,47 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L36" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M36" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:14">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N37" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:14">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>6</x:v>
@@ -1555,15 +1639,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:14">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>6</x:v>
@@ -1572,95 +1656,107 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M39" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:13">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:14">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L40" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M40" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N40" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:14">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L41" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M41" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N41" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:14">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L42" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N42" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:14">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L43" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M43" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N43" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:14">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>7</x:v>
@@ -1669,41 +1765,115 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L44" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:14">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M45" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:13">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N45" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:14">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D46" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M46" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N46" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:14">
+      <x:c r="A47" s="0">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M46" s="0" t="s">
-        <x:v>10</x:v>
+      <x:c r="N47" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:14">
+      <x:c r="A48" s="0">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D48" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N48" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:14">
+      <x:c r="A49" s="0">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D49" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N49" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:14">
+      <x:c r="A50" s="0">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N50" s="0" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
